--- a/W/A2Pico2LiteW_CPL.xlsx
+++ b/W/A2Pico2LiteW_CPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2Pico2LiteW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C35E81-5EE0-4D9E-A845-573956E319C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C599A2B-3376-4FAB-9389-13232D5EAB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t>Designator</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>C2</t>
-  </si>
-  <si>
-    <t>R3</t>
   </si>
 </sst>
 </file>
@@ -465,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.36328125" customWidth="1"/>
@@ -699,7 +696,7 @@
         <v>153.6446</v>
       </c>
       <c r="C10" s="2">
-        <v>-114.57940000000001</v>
+        <v>-116.71299999999999</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -717,19 +714,19 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2">
-        <v>153.6446</v>
+        <v>129.87020000000001</v>
       </c>
       <c r="C11" s="2">
-        <v>-116.71299999999999</v>
+        <v>-114.50320000000001</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="2">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -739,30 +736,6 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="2">
-        <v>129.87020000000001</v>
-      </c>
-      <c r="C12" s="2">
-        <v>-114.50320000000001</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="2">
-        <v>-90</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
